--- a/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RudolfEngelke\Documents\RStudio.wd\esqlabsR\inst\extdata\examples\TestProject\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B632CAB2-0D54-4784-8CBA-C6F6F21D18F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9EB25B-4B37-4801-84A3-F684DBB286FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2600" yWindow="1120" windowWidth="34360" windowHeight="19040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4910" yWindow="1390" windowWidth="27140" windowHeight="19040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
     <sheet name="OutputPaths" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>Scenario_name</t>
   </si>
@@ -92,9 +92,6 @@
     <t>0, 1, 60; 1, 12, 20</t>
   </si>
   <si>
-    <t>TRUE</t>
-  </si>
-  <si>
     <t>min</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t>TestPopulation</t>
   </si>
   <si>
-    <t>FALSE</t>
-  </si>
-  <si>
     <t>0, 12, 20</t>
   </si>
   <si>
@@ -125,10 +119,25 @@
     <t>PITestScenario</t>
   </si>
   <si>
+    <t>Aciclovir_PVB</t>
+  </si>
+  <si>
+    <t>PIScenario_250mg</t>
+  </si>
+  <si>
     <t>Aciclovir</t>
   </si>
   <si>
-    <t>Aciclovir_PVB</t>
+    <t>Protocol_250mg</t>
+  </si>
+  <si>
+    <t>0,120,1</t>
+  </si>
+  <si>
+    <t>PIScenario_500mg</t>
+  </si>
+  <si>
+    <t>Protocol_500mg</t>
   </si>
   <si>
     <t>OutputPathId</t>
@@ -150,9 +159,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -179,14 +196,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -199,9 +219,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -239,7 +259,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -311,7 +331,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -343,16 +363,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -474,99 +498,59 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="36.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.9140625" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -612,34 +596,34 @@
       <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" t="s">
-        <v>23</v>
+      <c r="I3" t="b">
+        <v>1</v>
       </c>
       <c r="J3">
         <v>500</v>
       </c>
       <c r="K3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
       </c>
       <c r="E4" t="s">
         <v>15</v>
@@ -648,13 +632,13 @@
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
         <v>18</v>
       </c>
-      <c r="I4" t="s">
-        <v>28</v>
+      <c r="I4" t="b">
+        <v>0</v>
       </c>
       <c r="L4" t="s">
         <v>19</v>
@@ -662,16 +646,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
@@ -680,13 +664,13 @@
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
         <v>18</v>
       </c>
-      <c r="I5" t="s">
-        <v>28</v>
+      <c r="I5" t="b">
+        <v>0</v>
       </c>
       <c r="L5" t="s">
         <v>19</v>
@@ -694,13 +678,13 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -717,59 +701,102 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
       </c>
       <c r="M7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
         <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:M2 A4:M7 A3:I3 K3:M3" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" t="s">
-        <v>37</v>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:B3" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
@@ -1,41 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="37920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
-    <sheet name="OutputPaths" sheetId="2" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OutputPaths" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+      <color indexed="81"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+      <b val="1"/>
+      <color indexed="81"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -54,17 +68,99 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Pavel Balazki</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Pavel Balazki:
+Simulation time is defined as time intervals.
+Expected is a triple of values {start, end, resolution}, resolution given in "points per &lt;time unit&gt;" as defined in the columne "SimulationTimeUnit". Multiple intervals can be separated by a ";"</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -78,44 +174,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -142,14 +238,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -176,6 +273,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -187,175 +285,170 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23.140625" customWidth="1" min="1" max="1"/>
+    <col width="11.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="14.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="23.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="22.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="18.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="19.140625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="11.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="16.140625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="20.140625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="13.7109375" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="30" bestFit="1" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Scenario_name</t>
@@ -411,12 +504,17 @@
           <t>SteadyStateTimeUnit</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OverwriteFormulasInSS</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ModelFile</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>OutputPathsIds</t>
         </is>
@@ -453,7 +551,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Aciclovir.pkml</t>
         </is>
@@ -493,7 +591,7 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>500</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -501,12 +599,12 @@
           <t>min</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Aciclovir.pkml</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Aciclovir_PVB, Aciclovir_fat_cell</t>
         </is>
@@ -554,7 +652,7 @@
       <c r="I4" t="b">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Aciclovir.pkml</t>
         </is>
@@ -602,7 +700,7 @@
       <c r="I5" t="b">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Aciclovir.pkml</t>
         </is>
@@ -639,7 +737,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Aciclovir.pkml</t>
         </is>
@@ -647,15 +745,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OutputPathId</t>
@@ -693,5 +801,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RudolfEngelke\Documents\RStudio.wd\esqlabsR\inst\extdata\examples\TestProject\Configurations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RudolfEngelke\Documents\RStudio.wd\esqlabsR.worktrees\pi-workflow\inst\extdata\examples\TestProject\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9EB25B-4B37-4801-84A3-F684DBB286FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7896360-A69B-4C18-B7CA-9BF5851A4DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4910" yWindow="1390" windowWidth="27140" windowHeight="19040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6950" yWindow="1300" windowWidth="27640" windowHeight="19270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
   <si>
     <t>Scenario_name</t>
   </si>
@@ -706,9 +706,6 @@
       <c r="L7" t="s">
         <v>19</v>
       </c>
-      <c r="M7" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -732,9 +729,6 @@
       <c r="L8" t="s">
         <v>19</v>
       </c>
-      <c r="M8" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -757,9 +751,6 @@
       </c>
       <c r="L9" t="s">
         <v>19</v>
-      </c>
-      <c r="M9" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub repositories\ESQlabs\esqlabsR\inst\extdata\examples\TestProject\Configurations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RudolfEngelke\Documents\RStudio.wd\esqlabsR.worktrees\update-aciclovir-pkml\inst\extdata\examples\TestProject\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F437A9AB-9A78-41D6-A0BE-980446BE39C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C66A711-427E-4337-901B-6EC532D0324A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="1450" windowWidth="27640" windowHeight="19270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="8" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
   <si>
     <t>SimulationTime</t>
   </si>
@@ -522,24 +522,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84A1BACA-04A5-4461-B34D-CB73BA82CEC5}">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -580,7 +580,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -602,8 +602,11 @@
       <c r="L2" t="s">
         <v>13</v>
       </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -638,7 +641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -670,7 +673,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>30</v>
       </c>
@@ -702,7 +705,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -735,13 +738,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA486CF-725F-421A-8D45-E3AE92A4A2C0}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
@@ -749,7 +752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -757,7 +760,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -772,6 +775,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="398d2b5b-77f8-4c5f-a794-3d35ce849315">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1c52e43a-7a2d-43c4-9ede-f251c929c0a1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010011DB5BA7A27696418C6D2C8B46A68E83" ma:contentTypeVersion="17" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="b3e823de345af38b5a0fa8b2c9729ead">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="398d2b5b-77f8-4c5f-a794-3d35ce849315" xmlns:ns3="1c52e43a-7a2d-43c4-9ede-f251c929c0a1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fae56da9623201e330c5b1623e145d1" ns2:_="" ns3:_="">
     <xsd:import namespace="398d2b5b-77f8-4c5f-a794-3d35ce849315"/>
@@ -1008,27 +1031,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="398d2b5b-77f8-4c5f-a794-3d35ce849315">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1c52e43a-7a2d-43c4-9ede-f251c929c0a1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46FCC551-4FF5-46A3-9024-D54BBA18C5A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2633B21-6509-4402-A676-EEE1878D6EA1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="398d2b5b-77f8-4c5f-a794-3d35ce849315"/>
+    <ds:schemaRef ds:uri="1c52e43a-7a2d-43c4-9ede-f251c929c0a1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB9A7DEF-8D50-4222-A255-A8C989265833}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1045,23 +1067,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2633B21-6509-4402-A676-EEE1878D6EA1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="398d2b5b-77f8-4c5f-a794-3d35ce849315"/>
-    <ds:schemaRef ds:uri="1c52e43a-7a2d-43c4-9ede-f251c929c0a1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46FCC551-4FF5-46A3-9024-D54BBA18C5A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
@@ -1,55 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="37920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="OutputPaths" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
+    <sheet name="OutputPaths" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -68,99 +54,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Pavel Balazki</author>
-  </authors>
-  <commentList>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Pavel Balazki:
-Simulation time is defined as time intervals.
-Expected is a triple of values {start, end, resolution}, resolution given in "points per &lt;time unit&gt;" as defined in the columne "SimulationTimeUnit". Multiple intervals can be separated by a ";"</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -174,44 +78,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -238,15 +142,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -273,7 +176,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -285,170 +187,175 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23.140625" customWidth="1" min="1" max="1"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="14.5703125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="23.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="22.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="18.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="19.140625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="11.5703125" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="16.140625" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="20.140625" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="13.7109375" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="30" bestFit="1" customWidth="1" min="13" max="13"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Scenario_name</t>
@@ -504,7 +411,7 @@
           <t>SteadyStateTimeUnit</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>OverwriteFormulasInSS</t>
         </is>
@@ -556,6 +463,11 @@
           <t>Aciclovir.pkml</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Aciclovir_PVB</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -591,7 +503,7 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>500</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -745,25 +657,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OutputPathId</t>
@@ -801,6 +703,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
@@ -1,44 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="21840" windowHeight="37920" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenarios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="OutputPaths" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
+    <sheet name="OutputPaths" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t xml:space="preserve">Aciclovir_PVB</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -63,81 +55,15 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -152,44 +78,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -216,15 +142,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -251,7 +176,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -263,170 +187,175 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="23.140625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="18.85546875" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="30" hidden="0" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Scenario_name</t>
@@ -482,7 +411,7 @@
           <t>SteadyStateTimeUnit</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>OverwriteFormulasInSS</t>
         </is>
@@ -534,8 +463,10 @@
           <t>Aciclovir.pkml</t>
         </is>
       </c>
-      <c r="N2" t="s">
-        <v>0</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Aciclovir_PVB</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -572,7 +503,7 @@
       <c r="I3" t="b">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>500</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -726,24 +657,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <cols>
-    <col min="1" max="1" width="16.28515625" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" hidden="0" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>OutputPathId</t>
@@ -781,6 +703,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Scenarios.xlsx
@@ -1,27 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RudolfEngelke\Documents\RStudio.wd\esqlabsR.worktrees\pi-workflow\inst\extdata\examples\TestProject\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E4FF0C-5C09-44C4-A351-7C0A443B5309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7460" yWindow="1190" windowWidth="27640" windowHeight="19270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7460" yWindow="1190" windowWidth="27640" windowHeight="19270" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
-    <sheet name="OutputPaths" sheetId="2" r:id="rId2"/>
+    <sheet name="OutputPaths" sheetId="2" state="visible" r:id="rId1"/>
+    <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>Scenario_name</t>
   </si>
@@ -153,13 +146,134 @@
   </si>
   <si>
     <t>Organism|Fat|Intracellular|Aciclovir|Concentration in container</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IndividualId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PopulationId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ReadPopulationFromCSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelParameterSheets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ApplicationProtocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SimulationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SimulationTimeUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SteadyState</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SteadyStateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SteadyStateTimeUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OverwriteFormulasInSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelFile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OutputPathsIds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestScenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indiv1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aciclovir_iv_250mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0, 24, 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aciclovir.pkml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aciclovir_PVB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestScenario2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Global", "Aciclovir", "Sheet, with comma"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0, 1, 60; 1, 12, 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aciclovir_PVB, Aciclovir_fat_cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PopulationScenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPopulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0, 12, 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PopulationScenarioFromCSV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestScenario_missingParam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global, MissingParam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PITestScenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIScenario_250mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aciclovir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protocol_250mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,120,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIScenario_500mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protocol_500mg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,12 +282,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -196,13 +315,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,296 +624,346 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" customWidth="1"/>
-    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>500</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>19</v>
+      <c r="B2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>43</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>500</v>
+      </c>
+      <c r="K3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L3"/>
+      <c r="M3" t="s">
+        <v>64</v>
+      </c>
+      <c r="N3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4" t="s">
+        <v>64</v>
+      </c>
+      <c r="N4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8" t="s">
+        <v>64</v>
+      </c>
+      <c r="N8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9"/>
+      <c r="C9"/>
+      <c r="D9"/>
+      <c r="E9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>